--- a/agreement_report.xlsx
+++ b/agreement_report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\cartera-inteligente-backend\src\CarteraInteligente.Web\resources\Accordances\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8F75DF-25D6-47F7-B38E-134F8BDA95B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{317B774B-02AD-42DD-A45A-F7AC6CE501EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1890" yWindow="0" windowWidth="26505" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="199">
   <si>
     <t>Reporte de Acuerdos</t>
   </si>
@@ -41,12 +41,15 @@
     <t>Tipo de acuerdo:</t>
   </si>
   <si>
+    <t>Revisión de Cartera</t>
+  </si>
+  <si>
+    <t>Región:</t>
+  </si>
+  <si>
     <t>Todos</t>
   </si>
   <si>
-    <t>Región:</t>
-  </si>
-  <si>
     <t>País:</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
     <t>3071/OC-CR</t>
   </si>
   <si>
-    <t>Revisión de Cartera</t>
-  </si>
-  <si>
     <t>TSP</t>
   </si>
   <si>
@@ -161,7 +161,7 @@
     <t>13/nov/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">La Unidad Ejecutora programará mediciones parciales de los indicadores de resultados del Programa asociadas con Barranca  Limonal y la Angostura en fechas que serán definidas mediante un cronograma a ser presentado por el MOPT al BID con copia al MH</t>
+    <t>La Unidad Ejecutora programará mediciones parciales de los indicadores de resultados del Programa asociadas con Barranca  Limonal y la Angostura en fechas que serán definidas mediante un cronograma a ser presentado por el MOPT al BID con copia al MH</t>
   </si>
   <si>
     <t>Plazo de desembolsos vencido o próximo a vencer</t>
@@ -549,13 +549,93 @@
   </si>
   <si>
     <t>Total acuerdos:</t>
+  </si>
+  <si>
+    <t>CR-L1024</t>
+  </si>
+  <si>
+    <t>2493/OC-CR</t>
+  </si>
+  <si>
+    <t>WSA</t>
+  </si>
+  <si>
+    <t>Programa de Agua Potable y Saneamiento</t>
+  </si>
+  <si>
+    <t>13/may/2024</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>Se requiere asegurar el financiamiento de colectores planeados para garantizar la continuidad del programa de saneamiento del area metropolitana de San José y obtener los resultados originalmente planteados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unidad Ejecutora y el AyA avanzarán con el plan financiero para la interconexión de obras construidas y no operativas, así como la conclusión de obras de la Etapa I del programa sanitario. </t>
+  </si>
+  <si>
+    <t>31/jul/2024</t>
+  </si>
+  <si>
+    <t>SILVIA</t>
+  </si>
+  <si>
+    <t>5x1/Inter-gerencial</t>
+  </si>
+  <si>
+    <t>01/jul/2022</t>
+  </si>
+  <si>
+    <t>Cumplidos</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">Tener un 10% del monto total comprometido para el 31 de diciembre de 2022. </t>
+  </si>
+  <si>
+    <t>31/dic/2022</t>
+  </si>
+  <si>
+    <t>ARNALDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>30/jun/2023</t>
+  </si>
+  <si>
+    <t>CR-L1070</t>
+  </si>
+  <si>
+    <t>3589/OC-CR</t>
+  </si>
+  <si>
+    <t>Primer Programa de Energía Renovable, Transmisión y Distribución de Electricidad</t>
+  </si>
+  <si>
+    <t>07/may/2024</t>
+  </si>
+  <si>
+    <t>Cancelados</t>
+  </si>
+  <si>
+    <t>Materiales para la reconstrucción de Línea de Transmisión Cañas-Guayabal 138kV</t>
+  </si>
+  <si>
+    <t>La Unidad Coordinadora ejecutará el programa de instalaciones dentro de los plazos acordados, a partir de las siguientes acciones:La UC firmará el contrato de Materiales para la reconstrucción de Línea de Transmisión Cañas- Guayabal 138kv y presentará un calendario detallado, incluyendo los plazos máximos ajustados y posibles riesgos.</t>
+  </si>
+  <si>
+    <t>08/sep/2024</t>
+  </si>
+  <si>
+    <t>SYLVIA VIRGINIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <sz val="10"/>
@@ -646,38 +726,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -942,151 +1022,150 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:Z44"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A2:Z47"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.59765625" customWidth="1"/>
-    <col min="2" max="2" width="16.1328125" customWidth="1"/>
-    <col min="3" max="3" width="16.1328125" customWidth="1"/>
-    <col min="4" max="4" width="18.86328125" customWidth="1"/>
-    <col min="5" max="5" width="19.3984375" customWidth="1"/>
-    <col min="6" max="6" width="19.1328125" customWidth="1"/>
-    <col min="7" max="7" width="43.3984375" customWidth="1"/>
-    <col min="8" max="8" width="20.86328125" customWidth="1"/>
-    <col min="9" max="9" width="24.1328125" customWidth="1"/>
-    <col min="10" max="11" width="29.59765625" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="43.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" customWidth="1"/>
+    <col min="10" max="11" width="29.5703125" customWidth="1"/>
     <col min="12" max="12" width="42" customWidth="1"/>
     <col min="13" max="14" width="44" customWidth="1"/>
     <col min="15" max="15" width="62" customWidth="1"/>
-    <col min="16" max="16" width="21.73046875" customWidth="1"/>
-    <col min="17" max="17" width="32.265625" customWidth="1"/>
-    <col min="18" max="19" width="39.59765625" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="32.28515625" customWidth="1"/>
+    <col min="18" max="19" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="45.75" customHeight="1">
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" ht="22.5">
-      <c r="B3" s="10" t="s">
+    <row r="2" spans="1:26" ht="45.75" customHeight="1">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:26" ht="23.25">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="5" ht="13.15">
+      <c r="C3" s="12"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="5" spans="1:26" ht="12.75">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="11"/>
+      <c r="D5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" ht="13.15">
+    <row r="6" spans="1:26" ht="12.75">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" ht="13.15">
+      <c r="D6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="1:26" ht="12.75">
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" ht="13.15">
+      <c r="D7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:26" ht="12.75">
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="10" ht="13.15" s="1" customFormat="1">
+      <c r="D8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="10" spans="1:26" s="1" customFormat="1" ht="12.75">
       <c r="B10" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="1" customFormat="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>29</v>
@@ -1134,18 +1213,18 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" spans="1:26" ht="36" customHeight="1">
       <c r="B12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>29</v>
@@ -1186,18 +1265,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" spans="1:26" ht="36" customHeight="1">
       <c r="B13" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>29</v>
@@ -1238,18 +1317,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" spans="1:26" ht="36" customHeight="1">
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>29</v>
@@ -1290,7 +1369,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" spans="1:26" ht="36" customHeight="1">
       <c r="B15" s="6" t="s">
         <v>49</v>
       </c>
@@ -1298,10 +1377,10 @@
         <v>50</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>29</v>
@@ -1342,7 +1421,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" spans="1:26" ht="36" customHeight="1">
       <c r="B16" s="6" t="s">
         <v>49</v>
       </c>
@@ -1350,10 +1429,10 @@
         <v>50</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>29</v>
@@ -1394,7 +1473,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" spans="2:19" ht="36" customHeight="1">
       <c r="B17" s="6" t="s">
         <v>62</v>
       </c>
@@ -1402,10 +1481,10 @@
         <v>63</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>29</v>
@@ -1446,7 +1525,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" spans="2:19" ht="36" customHeight="1">
       <c r="B18" s="6" t="s">
         <v>62</v>
       </c>
@@ -1454,10 +1533,10 @@
         <v>63</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>29</v>
@@ -1498,7 +1577,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" spans="2:19" ht="36" customHeight="1">
       <c r="B19" s="6" t="s">
         <v>62</v>
       </c>
@@ -1506,10 +1585,10 @@
         <v>63</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>29</v>
@@ -1550,7 +1629,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" spans="2:19" ht="36" customHeight="1">
       <c r="B20" s="6" t="s">
         <v>80</v>
       </c>
@@ -1558,10 +1637,10 @@
         <v>81</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>29</v>
@@ -1602,7 +1681,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" spans="2:19" ht="36" customHeight="1">
       <c r="B21" s="6" t="s">
         <v>80</v>
       </c>
@@ -1610,10 +1689,10 @@
         <v>81</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>29</v>
@@ -1654,7 +1733,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" spans="2:19" ht="36" customHeight="1">
       <c r="B22" s="6" t="s">
         <v>80</v>
       </c>
@@ -1662,10 +1741,10 @@
         <v>81</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>29</v>
@@ -1708,7 +1787,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" spans="2:19" ht="36" customHeight="1">
       <c r="B23" s="6" t="s">
         <v>95</v>
       </c>
@@ -1716,10 +1795,10 @@
         <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>97</v>
@@ -1760,7 +1839,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" spans="2:19" ht="36" customHeight="1">
       <c r="B24" s="6" t="s">
         <v>95</v>
       </c>
@@ -1768,10 +1847,10 @@
         <v>96</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>97</v>
@@ -1812,7 +1891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" spans="2:19" ht="36" customHeight="1">
       <c r="B25" s="6" t="s">
         <v>108</v>
       </c>
@@ -1820,10 +1899,10 @@
         <v>109</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>110</v>
@@ -1864,7 +1943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" spans="2:19" ht="36" customHeight="1">
       <c r="B26" s="6" t="s">
         <v>108</v>
       </c>
@@ -1872,10 +1951,10 @@
         <v>109</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>110</v>
@@ -1916,7 +1995,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" spans="2:19" ht="36" customHeight="1">
       <c r="B27" s="6" t="s">
         <v>108</v>
       </c>
@@ -1924,10 +2003,10 @@
         <v>109</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>110</v>
@@ -1968,7 +2047,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" spans="2:19" ht="36" customHeight="1">
       <c r="B28" s="6" t="s">
         <v>108</v>
       </c>
@@ -1976,10 +2055,10 @@
         <v>109</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>110</v>
@@ -2020,7 +2099,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" spans="2:19" ht="36" customHeight="1">
       <c r="B29" s="6" t="s">
         <v>125</v>
       </c>
@@ -2028,10 +2107,10 @@
         <v>126</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>127</v>
@@ -2072,7 +2151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" spans="2:19" ht="36" customHeight="1">
       <c r="B30" s="6" t="s">
         <v>125</v>
       </c>
@@ -2080,10 +2159,10 @@
         <v>126</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>127</v>
@@ -2124,7 +2203,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
+    <row r="31" spans="2:19" ht="36" customHeight="1">
       <c r="B31" s="6" t="s">
         <v>125</v>
       </c>
@@ -2132,10 +2211,10 @@
         <v>126</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>127</v>
@@ -2176,7 +2255,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" spans="2:19" ht="36" customHeight="1">
       <c r="B32" s="6" t="s">
         <v>139</v>
       </c>
@@ -2184,10 +2263,10 @@
         <v>140</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>141</v>
@@ -2228,7 +2307,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" spans="1:26" ht="36" customHeight="1">
       <c r="B33" s="6" t="s">
         <v>139</v>
       </c>
@@ -2236,10 +2315,10 @@
         <v>140</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>141</v>
@@ -2280,7 +2359,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" spans="1:26" ht="36" customHeight="1">
       <c r="B34" s="6" t="s">
         <v>139</v>
       </c>
@@ -2288,10 +2367,10 @@
         <v>140</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>141</v>
@@ -2332,7 +2411,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" spans="1:26" ht="36" customHeight="1">
       <c r="B35" s="6" t="s">
         <v>153</v>
       </c>
@@ -2340,10 +2419,10 @@
         <v>154</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>155</v>
@@ -2384,7 +2463,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
+    <row r="36" spans="1:26" ht="36" customHeight="1">
       <c r="B36" s="6" t="s">
         <v>153</v>
       </c>
@@ -2392,10 +2471,10 @@
         <v>154</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>155</v>
@@ -2436,7 +2515,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" spans="1:26" ht="36" customHeight="1">
       <c r="B37" s="6" t="s">
         <v>153</v>
       </c>
@@ -2444,10 +2523,10 @@
         <v>154</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>155</v>
@@ -2488,7 +2567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" spans="1:26" ht="36" customHeight="1">
       <c r="B38" s="6" t="s">
         <v>153</v>
       </c>
@@ -2496,10 +2575,10 @@
         <v>154</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>155</v>
@@ -2540,7 +2619,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" spans="1:26" ht="36" customHeight="1">
       <c r="B39" s="6" t="s">
         <v>153</v>
       </c>
@@ -2548,10 +2627,10 @@
         <v>154</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>155</v>
@@ -2592,47 +2671,203 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="B40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="B41" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="7"/>
-    </row>
-    <row r="42" ht="13.15">
-      <c r="B42" s="2" t="s">
+    <row r="40" spans="1:26" s="1" customFormat="1" ht="36" customHeight="1">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
+    </row>
+    <row r="41" spans="1:26" ht="36" customHeight="1">
+      <c r="B41" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="36" customHeight="1">
+      <c r="B42" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="7"/>
+    </row>
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
+      <c r="B44" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="7"/>
+    </row>
+    <row r="45" spans="1:26" ht="12.75">
+      <c r="B45" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="13">
+      <c r="C45" s="2"/>
+      <c r="D45" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="43" ht="13.15">
-      <c r="B43" s="2" t="s">
+    <row r="46" spans="1:26" ht="12.75">
+      <c r="B46" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="13">
+      <c r="C46" s="2"/>
+      <c r="D46" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="44" ht="13.15">
-      <c r="B44" s="2" t="s">
+    <row r="47" spans="1:26" ht="12.75">
+      <c r="B47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="13">
+      <c r="C47" s="2"/>
+      <c r="D47" s="9">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="6">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
@@ -2642,7 +2877,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/agreement_report.xlsx
+++ b/agreement_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{317B774B-02AD-42DD-A45A-F7AC6CE501EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{317B774B-02AD-42DD-A45A-F7AC6CE501EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00B4466A-F2AD-41C2-A012-9FEDB793B014}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="0" windowWidth="26505" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="2760" windowWidth="20805" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="172">
   <si>
     <t>Reporte de Acuerdos</t>
   </si>
@@ -549,87 +549,6 @@
   </si>
   <si>
     <t>Total acuerdos:</t>
-  </si>
-  <si>
-    <t>CR-L1024</t>
-  </si>
-  <si>
-    <t>2493/OC-CR</t>
-  </si>
-  <si>
-    <t>WSA</t>
-  </si>
-  <si>
-    <t>Programa de Agua Potable y Saneamiento</t>
-  </si>
-  <si>
-    <t>13/may/2024</t>
-  </si>
-  <si>
-    <t>Vigente</t>
-  </si>
-  <si>
-    <t>Se requiere asegurar el financiamiento de colectores planeados para garantizar la continuidad del programa de saneamiento del area metropolitana de San José y obtener los resultados originalmente planteados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Unidad Ejecutora y el AyA avanzarán con el plan financiero para la interconexión de obras construidas y no operativas, así como la conclusión de obras de la Etapa I del programa sanitario. </t>
-  </si>
-  <si>
-    <t>31/jul/2024</t>
-  </si>
-  <si>
-    <t>SILVIA</t>
-  </si>
-  <si>
-    <t>5x1/Inter-gerencial</t>
-  </si>
-  <si>
-    <t>01/jul/2022</t>
-  </si>
-  <si>
-    <t>Cumplidos</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">Tener un 10% del monto total comprometido para el 31 de diciembre de 2022. </t>
-  </si>
-  <si>
-    <t>31/dic/2022</t>
-  </si>
-  <si>
-    <t>ARNALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>30/jun/2023</t>
-  </si>
-  <si>
-    <t>CR-L1070</t>
-  </si>
-  <si>
-    <t>3589/OC-CR</t>
-  </si>
-  <si>
-    <t>Primer Programa de Energía Renovable, Transmisión y Distribución de Electricidad</t>
-  </si>
-  <si>
-    <t>07/may/2024</t>
-  </si>
-  <si>
-    <t>Cancelados</t>
-  </si>
-  <si>
-    <t>Materiales para la reconstrucción de Línea de Transmisión Cañas-Guayabal 138kV</t>
-  </si>
-  <si>
-    <t>La Unidad Coordinadora ejecutará el programa de instalaciones dentro de los plazos acordados, a partir de las siguientes acciones:La UC firmará el contrato de Materiales para la reconstrucción de Línea de Transmisión Cañas- Guayabal 138kv y presentará un calendario detallado, incluyendo los plazos máximos ajustados y posibles riesgos.</t>
-  </si>
-  <si>
-    <t>08/sep/2024</t>
-  </si>
-  <si>
-    <t>SYLVIA VIRGINIA</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +941,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:Z47"/>
+  <dimension ref="A2:Z44"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
@@ -2307,7 +2226,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="36" customHeight="1">
+    <row r="33" spans="2:19" ht="36" customHeight="1">
       <c r="B33" s="6" t="s">
         <v>139</v>
       </c>
@@ -2359,7 +2278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="36" customHeight="1">
+    <row r="34" spans="2:19" ht="36" customHeight="1">
       <c r="B34" s="6" t="s">
         <v>139</v>
       </c>
@@ -2411,7 +2330,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="36" customHeight="1">
+    <row r="35" spans="2:19" ht="36" customHeight="1">
       <c r="B35" s="6" t="s">
         <v>153</v>
       </c>
@@ -2463,7 +2382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="36" customHeight="1">
+    <row r="36" spans="2:19" ht="36" customHeight="1">
       <c r="B36" s="6" t="s">
         <v>153</v>
       </c>
@@ -2515,7 +2434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="36" customHeight="1">
+    <row r="37" spans="2:19" ht="36" customHeight="1">
       <c r="B37" s="6" t="s">
         <v>153</v>
       </c>
@@ -2567,7 +2486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="36" customHeight="1">
+    <row r="38" spans="2:19" ht="36" customHeight="1">
       <c r="B38" s="6" t="s">
         <v>153</v>
       </c>
@@ -2619,7 +2538,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="36" customHeight="1">
+    <row r="39" spans="2:19" ht="36" customHeight="1">
       <c r="B39" s="6" t="s">
         <v>153</v>
       </c>
@@ -2671,198 +2590,42 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:26" s="1" customFormat="1" ht="36" customHeight="1">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="5"/>
-      <c r="W40" s="5"/>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5"/>
-      <c r="Z40" s="5"/>
-    </row>
-    <row r="41" spans="1:26" ht="36" customHeight="1">
-      <c r="B41" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="P41" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" ht="36" customHeight="1">
-      <c r="B42" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q42" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B43" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="7"/>
-    </row>
-    <row r="45" spans="1:26" ht="12.75">
-      <c r="B45" s="2" t="s">
+    <row r="40" spans="2:19" ht="15.75" customHeight="1">
+      <c r="B40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" spans="2:19" ht="15.75" customHeight="1">
+      <c r="B41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="7"/>
+    </row>
+    <row r="42" spans="2:19" ht="12.75">
+      <c r="B42" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="9">
+      <c r="C42" s="2"/>
+      <c r="D42" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="12.75">
-      <c r="B46" s="2" t="s">
+    <row r="43" spans="2:19" ht="12.75">
+      <c r="B43" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="9">
+      <c r="C43" s="2"/>
+      <c r="D43" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="12.75">
-      <c r="B47" s="2" t="s">
+    <row r="44" spans="2:19" ht="12.75">
+      <c r="B44" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="9">
+      <c r="C44" s="2"/>
+      <c r="D44" s="9">
         <v>29</v>
       </c>
     </row>
